--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13060"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data Report" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="73">
   <si>
     <t>日期</t>
   </si>
@@ -35,6 +35,9 @@
     <t>计划</t>
   </si>
   <si>
+    <t>CampaignId</t>
+  </si>
+  <si>
     <t>消耗</t>
   </si>
   <si>
@@ -59,12 +62,21 @@
     <t>完成注册</t>
   </si>
   <si>
+    <t>预算</t>
+  </si>
+  <si>
     <t>date</t>
   </si>
   <si>
+    <t>Ad group</t>
+  </si>
+  <si>
     <t>Campaign</t>
   </si>
   <si>
+    <t>campaignId</t>
+  </si>
+  <si>
     <t>Cost</t>
   </si>
   <si>
@@ -89,6 +101,51 @@
     <t>CTR</t>
   </si>
   <si>
+    <t>Buget</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Optimization score</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Campaign type</t>
+  </si>
+  <si>
+    <t>View-through conv.</t>
+  </si>
+  <si>
+    <t>Particlpated in-app actions</t>
+  </si>
+  <si>
+    <t>Cost / Particlpated in-app actions</t>
+  </si>
+  <si>
+    <t>Conv. rate</t>
+  </si>
+  <si>
+    <t>Conversions</t>
+  </si>
+  <si>
+    <t>Cost / conv.</t>
+  </si>
+  <si>
+    <t>Target CPA</t>
+  </si>
+  <si>
+    <t>Brand Inclusions</t>
+  </si>
+  <si>
+    <t>Locations of interest</t>
+  </si>
+  <si>
+    <t>AdGroup</t>
+  </si>
+  <si>
     <t>campaign</t>
   </si>
   <si>
@@ -116,33 +173,94 @@
     <t>ctr</t>
   </si>
   <si>
+    <t>OptimizationScore</t>
+  </si>
+  <si>
+    <t>CampaignType</t>
+  </si>
+  <si>
+    <t>ViewThroughConv</t>
+  </si>
+  <si>
+    <t>ParticlpatedInAppActions</t>
+  </si>
+  <si>
+    <t>CostParticlpatedInAppActions</t>
+  </si>
+  <si>
+    <t>ConvRate</t>
+  </si>
+  <si>
+    <t>CostPerConv</t>
+  </si>
+  <si>
+    <t>TargetCPA</t>
+  </si>
+  <si>
+    <t>BrandInclusions</t>
+  </si>
+  <si>
+    <t>LocationsOfInterest</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
+    <t>sting</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>Ad group1</t>
+  </si>
+  <si>
     <t>印ZK3-304A-hwpg1343-0108-Leamahjning-FB-ID-kkluv</t>
   </si>
   <si>
+    <t>Eligible</t>
+  </si>
+  <si>
+    <t>1124-4-mcc</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>印ZK3-304A-hwpg1346-0122-Tujorialong-FB-ID-kkluv</t>
+  </si>
+  <si>
+    <t>23821392705</t>
+  </si>
+  <si>
+    <t>Paused</t>
+  </si>
+  <si>
+    <t>Removed</t>
+  </si>
+  <si>
+    <t>Pause</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -170,6 +288,19 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF3C4043"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -327,7 +458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,6 +468,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,28 +814,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,122 +835,131 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -808,53 +969,134 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1389,950 +1631,2357 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="27.4038461538462" style="3" customWidth="1"/>
-    <col min="2" max="2" width="62.2307692307692" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.4326923076923" style="3" customWidth="1"/>
-    <col min="4" max="5" width="23.4326923076923" style="4" customWidth="1"/>
-    <col min="6" max="7" width="23.4326923076923" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.0769230769231" style="3" customWidth="1"/>
-    <col min="9" max="9" width="28.625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.875" style="3" customWidth="1"/>
-    <col min="11" max="16363" width="12.7211538461538" style="3"/>
-    <col min="16364" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="27.4038461538462" style="4" customWidth="1"/>
+    <col min="3" max="3" width="62.2307692307692" style="3" customWidth="1"/>
+    <col min="4" max="4" width="43.2596153846154" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.4326923076923" style="3" customWidth="1"/>
+    <col min="6" max="7" width="23.4326923076923" style="6" customWidth="1"/>
+    <col min="8" max="9" width="23.4326923076923" style="3" customWidth="1"/>
+    <col min="10" max="10" width="18.0769230769231" style="3" customWidth="1"/>
+    <col min="11" max="11" width="28.625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="22.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.7211538461538" style="7"/>
+    <col min="14" max="14" width="12.7211538461538" style="8"/>
+    <col min="15" max="15" width="23.3942307692308" style="8" customWidth="1"/>
+    <col min="16" max="16" width="14.5769230769231" style="8" customWidth="1"/>
+    <col min="17" max="17" width="20.6730769230769" style="8" customWidth="1"/>
+    <col min="18" max="18" width="22.1153846153846" style="8" customWidth="1"/>
+    <col min="19" max="19" width="35.4134615384615" style="8" customWidth="1"/>
+    <col min="20" max="20" width="41.6634615384615" style="8" customWidth="1"/>
+    <col min="21" max="21" width="12.7211538461538" style="9"/>
+    <col min="22" max="22" width="14.0961538461538" style="9" customWidth="1"/>
+    <col min="23" max="23" width="14.4134615384615" style="8" customWidth="1"/>
+    <col min="24" max="24" width="21.1442307692308" style="7" customWidth="1"/>
+    <col min="25" max="25" width="16.8173076923077" style="3" customWidth="1"/>
+    <col min="26" max="26" width="24.3461538461538" style="3" customWidth="1"/>
+    <col min="27" max="16366" width="12.7211538461538" style="10"/>
+    <col min="16367" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:26">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
+      <c r="L1" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="21"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:10">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:26">
+      <c r="A2" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="W2" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="X2" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y2" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z2" s="30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:26">
+      <c r="A3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="U3" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="V3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="X3" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:26">
+      <c r="A4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="V4" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="W4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="X4" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z4" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="34">
+        <v>46147</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E5" s="37">
+        <v>105.42</v>
+      </c>
+      <c r="F5" s="38">
+        <v>22852</v>
+      </c>
+      <c r="G5" s="38">
+        <v>349</v>
+      </c>
+      <c r="H5" s="37">
+        <v>87</v>
+      </c>
+      <c r="I5" s="37">
+        <v>12</v>
+      </c>
+      <c r="J5" s="39">
+        <v>1.21</v>
+      </c>
+      <c r="K5" s="37">
+        <v>8.79</v>
+      </c>
+      <c r="L5" s="40">
+        <v>1.53</v>
+      </c>
+      <c r="M5" s="41">
+        <v>2</v>
+      </c>
+      <c r="N5" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P5" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" s="43">
+        <v>0</v>
+      </c>
+      <c r="S5" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T5" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U5" s="44">
+        <v>0.06</v>
+      </c>
+      <c r="V5" s="44">
+        <v>0</v>
+      </c>
+      <c r="W5" s="44">
+        <v>0</v>
+      </c>
+      <c r="X5" s="41">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="Y5" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z5" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="34">
+        <v>46148</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="37">
+        <v>96.23</v>
+      </c>
+      <c r="F6" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G6" s="38">
+        <v>128</v>
+      </c>
+      <c r="H6" s="37">
+        <v>27</v>
+      </c>
+      <c r="I6" s="37">
+        <v>10</v>
+      </c>
+      <c r="J6" s="37">
+        <v>4</v>
+      </c>
+      <c r="K6" s="37">
+        <v>4.7</v>
+      </c>
+      <c r="L6" s="40">
+        <v>2.71</v>
+      </c>
+      <c r="M6" s="41">
+        <v>2</v>
+      </c>
+      <c r="N6" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P6" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R6" s="43">
+        <v>0</v>
+      </c>
+      <c r="S6" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T6" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U6" s="44">
+        <v>1.06</v>
+      </c>
+      <c r="V6" s="44">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44">
+        <v>0</v>
+      </c>
+      <c r="X6" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z6" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="34">
+        <v>46146</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E7" s="37">
+        <v>389.32</v>
+      </c>
+      <c r="F7" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="38">
+        <v>517</v>
+      </c>
+      <c r="H7" s="37">
+        <v>86</v>
+      </c>
+      <c r="I7" s="37">
+        <v>46</v>
+      </c>
+      <c r="J7" s="37">
+        <v>23</v>
+      </c>
+      <c r="K7" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L7" s="40">
+        <v>2.67</v>
+      </c>
+      <c r="M7" s="41">
+        <v>2</v>
+      </c>
+      <c r="N7" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P7" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" s="43">
+        <v>0</v>
+      </c>
+      <c r="S7" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T7" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U7" s="44">
+        <v>2.06</v>
+      </c>
+      <c r="V7" s="44">
+        <v>0</v>
+      </c>
+      <c r="W7" s="44">
+        <v>0</v>
+      </c>
+      <c r="X7" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="34">
+        <v>46146</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E8" s="37">
+        <v>201.66</v>
+      </c>
+      <c r="F8" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G8" s="38">
+        <v>3241</v>
+      </c>
+      <c r="H8" s="37">
+        <v>3358</v>
+      </c>
+      <c r="I8" s="37">
+        <v>2216</v>
+      </c>
+      <c r="J8" s="37">
+        <v>633329</v>
+      </c>
+      <c r="K8" s="37">
+        <v>33226.18</v>
+      </c>
+      <c r="L8" s="40">
+        <v>2.63</v>
+      </c>
+      <c r="M8" s="41">
+        <v>2</v>
+      </c>
+      <c r="N8" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" s="43">
+        <v>0</v>
+      </c>
+      <c r="S8" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T8" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U8" s="44">
+        <v>3.06</v>
+      </c>
+      <c r="V8" s="44">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44">
+        <v>0</v>
+      </c>
+      <c r="X8" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z8" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="34">
+        <v>46148</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E9" s="37">
+        <v>360.58</v>
+      </c>
+      <c r="F9" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="38">
+        <v>5483</v>
+      </c>
+      <c r="H9" s="37">
+        <v>62107</v>
+      </c>
+      <c r="I9" s="37">
+        <v>55350</v>
+      </c>
+      <c r="J9" s="37">
+        <v>17</v>
+      </c>
+      <c r="K9" s="37">
+        <v>4.7</v>
+      </c>
+      <c r="L9" s="40">
+        <v>2.59</v>
+      </c>
+      <c r="M9" s="41">
+        <v>2</v>
+      </c>
+      <c r="N9" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P9" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="43">
+        <v>0</v>
+      </c>
+      <c r="S9" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T9" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U9" s="44">
+        <v>4.06</v>
+      </c>
+      <c r="V9" s="44">
+        <v>0</v>
+      </c>
+      <c r="W9" s="44">
+        <v>0</v>
+      </c>
+      <c r="X9" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z9" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" s="34">
+        <v>46143</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E10" s="37">
+        <v>170.59</v>
+      </c>
+      <c r="F10" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G10" s="38">
+        <v>1200</v>
+      </c>
+      <c r="H10" s="37">
+        <v>45</v>
+      </c>
+      <c r="I10" s="37">
+        <v>9</v>
+      </c>
+      <c r="J10" s="37">
+        <v>5</v>
+      </c>
+      <c r="K10" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L10" s="40">
+        <v>2.55</v>
+      </c>
+      <c r="M10" s="41">
+        <v>2</v>
+      </c>
+      <c r="N10" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P10" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="43">
+        <v>0</v>
+      </c>
+      <c r="S10" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T10" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U10" s="44">
+        <v>5.06</v>
+      </c>
+      <c r="V10" s="44">
+        <v>0</v>
+      </c>
+      <c r="W10" s="44">
+        <v>0</v>
+      </c>
+      <c r="X10" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z10" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="34">
+        <v>46143</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E11" s="37">
+        <v>427.82</v>
+      </c>
+      <c r="F11" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="38">
+        <v>517</v>
+      </c>
+      <c r="H11" s="37">
+        <v>102</v>
+      </c>
+      <c r="I11" s="37">
+        <v>59</v>
+      </c>
+      <c r="J11" s="37">
+        <v>27</v>
+      </c>
+      <c r="K11" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L11" s="40">
+        <v>2.51</v>
+      </c>
+      <c r="M11" s="41">
+        <v>2</v>
+      </c>
+      <c r="N11" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P11" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" s="43">
+        <v>0</v>
+      </c>
+      <c r="S11" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T11" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U11" s="44">
+        <v>6.06</v>
+      </c>
+      <c r="V11" s="44">
+        <v>0</v>
+      </c>
+      <c r="W11" s="44">
+        <v>0</v>
+      </c>
+      <c r="X11" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z11" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="34">
+        <v>46144</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E12" s="37">
+        <v>212.92</v>
+      </c>
+      <c r="F12" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G12" s="38">
+        <v>210</v>
+      </c>
+      <c r="H12" s="37">
+        <v>39</v>
+      </c>
+      <c r="I12" s="37">
         <v>12</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="J12" s="37">
+        <v>7</v>
+      </c>
+      <c r="K12" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L12" s="40">
+        <v>2.47</v>
+      </c>
+      <c r="M12" s="41">
+        <v>2</v>
+      </c>
+      <c r="N12" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P12" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R12" s="43">
+        <v>0</v>
+      </c>
+      <c r="S12" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T12" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U12" s="44">
+        <v>7.06</v>
+      </c>
+      <c r="V12" s="44">
+        <v>0</v>
+      </c>
+      <c r="W12" s="44">
+        <v>0</v>
+      </c>
+      <c r="X12" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z12" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="34">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E13" s="37">
+        <v>446.02</v>
+      </c>
+      <c r="F13" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="38">
+        <v>500</v>
+      </c>
+      <c r="H13" s="37">
+        <v>123</v>
+      </c>
+      <c r="I13" s="37">
+        <v>46</v>
+      </c>
+      <c r="J13" s="37">
         <v>14</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>19</v>
+      <c r="K13" s="37">
+        <v>4.7</v>
+      </c>
+      <c r="L13" s="40">
+        <v>2.43</v>
+      </c>
+      <c r="M13" s="41">
+        <v>2</v>
+      </c>
+      <c r="N13" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O13" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P13" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q13" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R13" s="43">
+        <v>0</v>
+      </c>
+      <c r="S13" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T13" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U13" s="44">
+        <v>8.06</v>
+      </c>
+      <c r="V13" s="44">
+        <v>0</v>
+      </c>
+      <c r="W13" s="44">
+        <v>0</v>
+      </c>
+      <c r="X13" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z13" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:10">
-      <c r="A3" s="9" t="s">
+    <row r="14" spans="1:26">
+      <c r="A14" s="34">
+        <v>46148</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E14" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F14" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G14" s="38">
+        <v>322</v>
+      </c>
+      <c r="H14" s="37">
+        <v>56</v>
+      </c>
+      <c r="I14" s="37">
+        <v>9</v>
+      </c>
+      <c r="J14" s="37">
+        <v>7</v>
+      </c>
+      <c r="K14" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L14" s="40">
+        <v>2.39</v>
+      </c>
+      <c r="M14" s="41">
+        <v>2</v>
+      </c>
+      <c r="N14" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P14" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q14" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" s="43">
+        <v>0</v>
+      </c>
+      <c r="S14" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T14" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U14" s="44">
+        <v>9.06</v>
+      </c>
+      <c r="V14" s="44">
+        <v>0</v>
+      </c>
+      <c r="W14" s="44">
+        <v>0</v>
+      </c>
+      <c r="X14" s="41">
         <v>10</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="Y14" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z14" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="A15" s="34">
+        <v>46144</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E15" s="37">
+        <v>427.82</v>
+      </c>
+      <c r="F15" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="38">
+        <v>517</v>
+      </c>
+      <c r="H15" s="37">
+        <v>102</v>
+      </c>
+      <c r="I15" s="37">
+        <v>59</v>
+      </c>
+      <c r="J15" s="37">
         <v>27</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>28</v>
+      <c r="K15" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L15" s="40">
+        <v>2.51</v>
+      </c>
+      <c r="M15" s="41">
+        <v>2</v>
+      </c>
+      <c r="N15" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O15" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P15" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q15" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R15" s="43">
+        <v>0</v>
+      </c>
+      <c r="S15" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T15" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U15" s="44">
+        <v>10.06</v>
+      </c>
+      <c r="V15" s="44">
+        <v>0</v>
+      </c>
+      <c r="W15" s="44">
+        <v>0</v>
+      </c>
+      <c r="X15" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z15" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:10">
-      <c r="A4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>30</v>
+    <row r="16" spans="1:26">
+      <c r="A16" s="34">
+        <v>46146</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E16" s="37">
+        <v>212.92</v>
+      </c>
+      <c r="F16" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G16" s="38">
+        <v>210</v>
+      </c>
+      <c r="H16" s="37">
+        <v>39</v>
+      </c>
+      <c r="I16" s="37">
+        <v>12</v>
+      </c>
+      <c r="J16" s="37">
+        <v>7</v>
+      </c>
+      <c r="K16" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L16" s="40">
+        <v>2.47</v>
+      </c>
+      <c r="M16" s="41">
+        <v>2</v>
+      </c>
+      <c r="N16" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O16" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P16" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R16" s="43">
+        <v>0</v>
+      </c>
+      <c r="S16" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T16" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U16" s="44">
+        <v>11.06</v>
+      </c>
+      <c r="V16" s="44">
+        <v>0</v>
+      </c>
+      <c r="W16" s="44">
+        <v>0</v>
+      </c>
+      <c r="X16" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z16" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="13">
+    <row r="17" spans="1:26">
+      <c r="A17" s="34">
         <v>46147</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="15">
-        <v>105.42</v>
-      </c>
-      <c r="D5" s="16">
-        <v>22852</v>
-      </c>
-      <c r="E5" s="16">
-        <v>349</v>
-      </c>
-      <c r="F5" s="15">
-        <v>87</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="B17" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E17" s="37">
+        <v>446.02</v>
+      </c>
+      <c r="F17" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="38">
+        <v>500</v>
+      </c>
+      <c r="H17" s="37">
+        <v>123</v>
+      </c>
+      <c r="I17" s="37">
+        <v>46</v>
+      </c>
+      <c r="J17" s="37">
+        <v>14</v>
+      </c>
+      <c r="K17" s="37">
+        <v>4.7</v>
+      </c>
+      <c r="L17" s="40">
+        <v>2.43</v>
+      </c>
+      <c r="M17" s="41">
+        <v>2</v>
+      </c>
+      <c r="N17" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O17" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P17" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q17" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R17" s="43">
+        <v>0</v>
+      </c>
+      <c r="S17" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T17" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U17" s="44">
+        <v>12.06</v>
+      </c>
+      <c r="V17" s="44">
+        <v>0</v>
+      </c>
+      <c r="W17" s="44">
+        <v>0</v>
+      </c>
+      <c r="X17" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y17" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z17" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" s="34">
+        <v>46144</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E18" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F18" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G18" s="38">
+        <v>322</v>
+      </c>
+      <c r="H18" s="37">
+        <v>56</v>
+      </c>
+      <c r="I18" s="37">
+        <v>9</v>
+      </c>
+      <c r="J18" s="37">
+        <v>7</v>
+      </c>
+      <c r="K18" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L18" s="40">
+        <v>2.39</v>
+      </c>
+      <c r="M18" s="41">
+        <v>2</v>
+      </c>
+      <c r="N18" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O18" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P18" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R18" s="43">
+        <v>0</v>
+      </c>
+      <c r="S18" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T18" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U18" s="44">
+        <v>13.06</v>
+      </c>
+      <c r="V18" s="44">
+        <v>0</v>
+      </c>
+      <c r="W18" s="44">
+        <v>0</v>
+      </c>
+      <c r="X18" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y18" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z18" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="34">
+        <v>46142</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E19" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F19" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G19" s="38">
+        <v>322</v>
+      </c>
+      <c r="H19" s="37">
+        <v>56</v>
+      </c>
+      <c r="I19" s="37">
+        <v>9</v>
+      </c>
+      <c r="J19" s="37">
+        <v>7</v>
+      </c>
+      <c r="K19" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L19" s="40">
+        <v>2.39</v>
+      </c>
+      <c r="M19" s="41">
+        <v>2</v>
+      </c>
+      <c r="N19" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O19" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P19" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R19" s="43">
+        <v>0</v>
+      </c>
+      <c r="S19" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T19" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U19" s="44">
+        <v>14.06</v>
+      </c>
+      <c r="V19" s="44">
+        <v>0</v>
+      </c>
+      <c r="W19" s="44">
+        <v>0</v>
+      </c>
+      <c r="X19" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z19" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="A20" s="34">
+        <v>46132</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E20" s="37">
+        <v>427.82</v>
+      </c>
+      <c r="F20" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="38">
+        <v>517</v>
+      </c>
+      <c r="H20" s="37">
+        <v>102</v>
+      </c>
+      <c r="I20" s="37">
+        <v>59</v>
+      </c>
+      <c r="J20" s="37">
+        <v>27</v>
+      </c>
+      <c r="K20" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L20" s="40">
+        <v>2.51</v>
+      </c>
+      <c r="M20" s="41">
+        <v>2</v>
+      </c>
+      <c r="N20" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O20" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P20" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R20" s="43">
+        <v>0</v>
+      </c>
+      <c r="S20" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T20" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U20" s="44">
+        <v>15.06</v>
+      </c>
+      <c r="V20" s="44">
+        <v>0</v>
+      </c>
+      <c r="W20" s="44">
+        <v>0</v>
+      </c>
+      <c r="X20" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z20" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
+      <c r="A21" s="34">
+        <v>46145</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E21" s="37">
+        <v>212.92</v>
+      </c>
+      <c r="F21" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G21" s="38">
+        <v>210</v>
+      </c>
+      <c r="H21" s="37">
+        <v>39</v>
+      </c>
+      <c r="I21" s="37">
         <v>12</v>
       </c>
-      <c r="H5" s="17">
-        <v>1.21</v>
-      </c>
-      <c r="I5" s="15">
-        <v>8.79</v>
-      </c>
-      <c r="J5" s="18">
-        <v>1.53</v>
+      <c r="J21" s="37">
+        <v>7</v>
+      </c>
+      <c r="K21" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L21" s="40">
+        <v>2.47</v>
+      </c>
+      <c r="M21" s="41">
+        <v>2</v>
+      </c>
+      <c r="N21" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="O21" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P21" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R21" s="43">
+        <v>0</v>
+      </c>
+      <c r="S21" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T21" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U21" s="44">
+        <v>16.06</v>
+      </c>
+      <c r="V21" s="44">
+        <v>0</v>
+      </c>
+      <c r="W21" s="44">
+        <v>0</v>
+      </c>
+      <c r="X21" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z21" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="13">
+    <row r="22" spans="1:26">
+      <c r="A22" s="34">
         <v>46148</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="15">
-        <v>96.23</v>
-      </c>
-      <c r="D6" s="16">
+      <c r="B22" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E22" s="37">
+        <v>446.02</v>
+      </c>
+      <c r="F22" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="38">
+        <v>500</v>
+      </c>
+      <c r="H22" s="37">
+        <v>123</v>
+      </c>
+      <c r="I22" s="37">
+        <v>46</v>
+      </c>
+      <c r="J22" s="37">
+        <v>14</v>
+      </c>
+      <c r="K22" s="37">
+        <v>4.7</v>
+      </c>
+      <c r="L22" s="40">
+        <v>2.43</v>
+      </c>
+      <c r="M22" s="41">
+        <v>2</v>
+      </c>
+      <c r="N22" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="O22" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P22" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q22" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R22" s="43">
+        <v>0</v>
+      </c>
+      <c r="S22" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T22" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U22" s="44">
+        <v>17.06</v>
+      </c>
+      <c r="V22" s="44">
+        <v>0</v>
+      </c>
+      <c r="W22" s="44">
+        <v>0</v>
+      </c>
+      <c r="X22" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z22" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" s="34">
+        <v>46137</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E23" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F23" s="38">
         <v>1200</v>
       </c>
-      <c r="E6" s="16">
-        <v>128</v>
-      </c>
-      <c r="F6" s="15">
+      <c r="G23" s="38">
+        <v>322</v>
+      </c>
+      <c r="H23" s="37">
+        <v>56</v>
+      </c>
+      <c r="I23" s="37">
+        <v>9</v>
+      </c>
+      <c r="J23" s="37">
+        <v>7</v>
+      </c>
+      <c r="K23" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L23" s="40">
+        <v>2.39</v>
+      </c>
+      <c r="M23" s="41">
+        <v>2</v>
+      </c>
+      <c r="N23" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P23" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q23" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R23" s="43">
+        <v>0</v>
+      </c>
+      <c r="S23" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T23" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U23" s="44">
+        <v>18.06</v>
+      </c>
+      <c r="V23" s="44">
+        <v>0</v>
+      </c>
+      <c r="W23" s="44">
+        <v>0</v>
+      </c>
+      <c r="X23" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y23" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z23" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
+      <c r="A24" s="34">
+        <v>46140</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E24" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F24" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G24" s="38">
+        <v>322</v>
+      </c>
+      <c r="H24" s="37">
+        <v>56</v>
+      </c>
+      <c r="I24" s="37">
+        <v>9</v>
+      </c>
+      <c r="J24" s="37">
+        <v>7</v>
+      </c>
+      <c r="K24" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L24" s="40">
+        <v>2.39</v>
+      </c>
+      <c r="M24" s="41">
+        <v>2</v>
+      </c>
+      <c r="N24" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O24" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P24" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q24" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R24" s="43">
+        <v>0</v>
+      </c>
+      <c r="S24" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T24" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U24" s="44">
+        <v>19.06</v>
+      </c>
+      <c r="V24" s="44">
+        <v>0</v>
+      </c>
+      <c r="W24" s="44">
+        <v>0</v>
+      </c>
+      <c r="X24" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y24" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z24" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" s="34">
+        <v>46140</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E25" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F25" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G25" s="38">
+        <v>322</v>
+      </c>
+      <c r="H25" s="37">
+        <v>56</v>
+      </c>
+      <c r="I25" s="37">
+        <v>9</v>
+      </c>
+      <c r="J25" s="37">
+        <v>7</v>
+      </c>
+      <c r="K25" s="37">
+        <v>5.31</v>
+      </c>
+      <c r="L25" s="40">
+        <v>2.39</v>
+      </c>
+      <c r="M25" s="41">
+        <v>2</v>
+      </c>
+      <c r="N25" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O25" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P25" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q25" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R25" s="43">
+        <v>0</v>
+      </c>
+      <c r="S25" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T25" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U25" s="44">
+        <v>20.06</v>
+      </c>
+      <c r="V25" s="44">
+        <v>0</v>
+      </c>
+      <c r="W25" s="44">
+        <v>0</v>
+      </c>
+      <c r="X25" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y25" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z25" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26">
+      <c r="A26" s="34">
+        <v>46136</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E26" s="37">
+        <v>427.82</v>
+      </c>
+      <c r="F26" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="38">
+        <v>517</v>
+      </c>
+      <c r="H26" s="37">
+        <v>102</v>
+      </c>
+      <c r="I26" s="37">
+        <v>59</v>
+      </c>
+      <c r="J26" s="37">
         <v>27</v>
       </c>
-      <c r="G6" s="15">
+      <c r="K26" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L26" s="40">
+        <v>2.51</v>
+      </c>
+      <c r="M26" s="41">
+        <v>2</v>
+      </c>
+      <c r="N26" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O26" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P26" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q26" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R26" s="43">
+        <v>0</v>
+      </c>
+      <c r="S26" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T26" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U26" s="44">
+        <v>21.06</v>
+      </c>
+      <c r="V26" s="44">
+        <v>0</v>
+      </c>
+      <c r="W26" s="44">
+        <v>0</v>
+      </c>
+      <c r="X26" s="41">
         <v>10</v>
       </c>
-      <c r="H6" s="15">
-        <v>4</v>
-      </c>
-      <c r="I6" s="15">
+      <c r="Y26" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z26" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
+      <c r="A27" s="34">
+        <v>46141</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E27" s="37">
+        <v>212.92</v>
+      </c>
+      <c r="F27" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="38">
+        <v>210</v>
+      </c>
+      <c r="H27" s="37">
+        <v>39</v>
+      </c>
+      <c r="I27" s="37">
+        <v>12</v>
+      </c>
+      <c r="J27" s="37">
+        <v>7</v>
+      </c>
+      <c r="K27" s="37">
+        <v>6.18</v>
+      </c>
+      <c r="L27" s="40">
+        <v>2.47</v>
+      </c>
+      <c r="M27" s="41">
+        <v>2</v>
+      </c>
+      <c r="N27" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P27" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q27" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R27" s="43">
+        <v>0</v>
+      </c>
+      <c r="S27" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T27" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U27" s="44">
+        <v>22.06</v>
+      </c>
+      <c r="V27" s="44">
+        <v>0</v>
+      </c>
+      <c r="W27" s="44">
+        <v>0</v>
+      </c>
+      <c r="X27" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y27" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z27" s="45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="A28" s="34">
+        <v>46138</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E28" s="37">
+        <v>446.02</v>
+      </c>
+      <c r="F28" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G28" s="38">
+        <v>500</v>
+      </c>
+      <c r="H28" s="37">
+        <v>123</v>
+      </c>
+      <c r="I28" s="37">
+        <v>46</v>
+      </c>
+      <c r="J28" s="37">
+        <v>14</v>
+      </c>
+      <c r="K28" s="37">
         <v>4.7</v>
       </c>
-      <c r="J6" s="18">
-        <v>2.71</v>
+      <c r="L28" s="40">
+        <v>2.43</v>
+      </c>
+      <c r="M28" s="41">
+        <v>2</v>
+      </c>
+      <c r="N28" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P28" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q28" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R28" s="43">
+        <v>0</v>
+      </c>
+      <c r="S28" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T28" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U28" s="44">
+        <v>23.06</v>
+      </c>
+      <c r="V28" s="44">
+        <v>0</v>
+      </c>
+      <c r="W28" s="44">
+        <v>0</v>
+      </c>
+      <c r="X28" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y28" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z28" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="13">
-        <v>46146</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="15">
-        <v>389.32</v>
-      </c>
-      <c r="D7" s="16">
-        <v>20001000</v>
-      </c>
-      <c r="E7" s="16">
-        <v>517</v>
-      </c>
-      <c r="F7" s="15">
-        <v>86</v>
-      </c>
-      <c r="G7" s="15">
-        <v>46</v>
-      </c>
-      <c r="H7" s="15">
-        <v>23</v>
-      </c>
-      <c r="I7" s="15">
+    <row r="29" spans="1:26">
+      <c r="A29" s="34">
+        <v>46136</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="14">
+        <v>23821392705</v>
+      </c>
+      <c r="E29" s="37">
+        <v>337.91</v>
+      </c>
+      <c r="F29" s="38">
+        <v>1200</v>
+      </c>
+      <c r="G29" s="38">
+        <v>322</v>
+      </c>
+      <c r="H29" s="37">
+        <v>56</v>
+      </c>
+      <c r="I29" s="37">
+        <v>9</v>
+      </c>
+      <c r="J29" s="37">
+        <v>7</v>
+      </c>
+      <c r="K29" s="37">
         <v>5.31</v>
       </c>
-      <c r="J7" s="18">
-        <v>2.67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="13">
-        <v>46146</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="15">
-        <v>2234201.66</v>
-      </c>
-      <c r="D8" s="16">
-        <v>300001200</v>
-      </c>
-      <c r="E8" s="16">
-        <v>37633241</v>
-      </c>
-      <c r="F8" s="15">
-        <v>352233358</v>
-      </c>
-      <c r="G8" s="15">
-        <v>11112216</v>
-      </c>
-      <c r="H8" s="15">
-        <v>3256633329</v>
-      </c>
-      <c r="I8" s="15">
-        <v>4446233226.18</v>
-      </c>
-      <c r="J8" s="18">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="13">
-        <v>46148</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="15">
-        <v>2123360.58</v>
-      </c>
-      <c r="D9" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E9" s="16">
-        <v>987445483</v>
-      </c>
-      <c r="F9" s="15">
-        <v>4446462107</v>
-      </c>
-      <c r="G9" s="15">
-        <v>332355350</v>
-      </c>
-      <c r="H9" s="15">
-        <v>17</v>
-      </c>
-      <c r="I9" s="15">
-        <v>4.7</v>
-      </c>
-      <c r="J9" s="18">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="13">
-        <v>46143</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="15">
-        <v>170.59</v>
-      </c>
-      <c r="D10" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E10" s="16">
-        <v>188</v>
-      </c>
-      <c r="F10" s="15">
-        <v>45</v>
-      </c>
-      <c r="G10" s="15">
-        <v>9</v>
-      </c>
-      <c r="H10" s="15">
-        <v>5</v>
-      </c>
-      <c r="I10" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J10" s="18">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="13">
-        <v>46143</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="15">
-        <v>427.82</v>
-      </c>
-      <c r="D11" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="16">
-        <v>517</v>
-      </c>
-      <c r="F11" s="15">
-        <v>102</v>
-      </c>
-      <c r="G11" s="15">
-        <v>59</v>
-      </c>
-      <c r="H11" s="15">
-        <v>27</v>
-      </c>
-      <c r="I11" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J11" s="18">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="13">
-        <v>46144</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="15">
-        <v>212.92</v>
-      </c>
-      <c r="D12" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E12" s="16">
-        <v>210</v>
-      </c>
-      <c r="F12" s="15">
-        <v>39</v>
-      </c>
-      <c r="G12" s="15">
-        <v>12</v>
-      </c>
-      <c r="H12" s="15">
-        <v>7</v>
-      </c>
-      <c r="I12" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J12" s="18">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="13">
-        <v>46148</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="15">
-        <v>446.02</v>
-      </c>
-      <c r="D13" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E13" s="16">
-        <v>500</v>
-      </c>
-      <c r="F13" s="15">
-        <v>123</v>
-      </c>
-      <c r="G13" s="15">
-        <v>46</v>
-      </c>
-      <c r="H13" s="15">
-        <v>14</v>
-      </c>
-      <c r="I13" s="15">
-        <v>4.7</v>
-      </c>
-      <c r="J13" s="18">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="13">
-        <v>46148</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D14" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E14" s="16">
-        <v>322</v>
-      </c>
-      <c r="F14" s="15">
-        <v>56</v>
-      </c>
-      <c r="G14" s="15">
-        <v>9</v>
-      </c>
-      <c r="H14" s="15">
-        <v>7</v>
-      </c>
-      <c r="I14" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J14" s="18">
+      <c r="L29" s="40">
         <v>2.39</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="13">
-        <v>46144</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="15">
-        <v>427.82</v>
-      </c>
-      <c r="D15" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E15" s="16">
-        <v>517</v>
-      </c>
-      <c r="F15" s="15">
-        <v>102</v>
-      </c>
-      <c r="G15" s="15">
-        <v>59</v>
-      </c>
-      <c r="H15" s="15">
-        <v>27</v>
-      </c>
-      <c r="I15" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J15" s="18">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="13">
-        <v>46146</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="15">
-        <v>212.92</v>
-      </c>
-      <c r="D16" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E16" s="16">
-        <v>210</v>
-      </c>
-      <c r="F16" s="15">
-        <v>39</v>
-      </c>
-      <c r="G16" s="15">
-        <v>12</v>
-      </c>
-      <c r="H16" s="15">
-        <v>7</v>
-      </c>
-      <c r="I16" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J16" s="18">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="13">
-        <v>46147</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="15">
-        <v>446.02</v>
-      </c>
-      <c r="D17" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E17" s="16">
-        <v>500</v>
-      </c>
-      <c r="F17" s="15">
-        <v>123</v>
-      </c>
-      <c r="G17" s="15">
-        <v>46</v>
-      </c>
-      <c r="H17" s="15">
-        <v>14</v>
-      </c>
-      <c r="I17" s="15">
-        <v>4.7</v>
-      </c>
-      <c r="J17" s="18">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="13">
-        <v>46144</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D18" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E18" s="16">
-        <v>322</v>
-      </c>
-      <c r="F18" s="15">
-        <v>56</v>
-      </c>
-      <c r="G18" s="15">
-        <v>9</v>
-      </c>
-      <c r="H18" s="15">
-        <v>7</v>
-      </c>
-      <c r="I18" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J18" s="18">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="13">
-        <v>46142</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D19" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E19" s="16">
-        <v>322</v>
-      </c>
-      <c r="F19" s="15">
-        <v>56</v>
-      </c>
-      <c r="G19" s="15">
-        <v>9</v>
-      </c>
-      <c r="H19" s="15">
-        <v>7</v>
-      </c>
-      <c r="I19" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J19" s="18">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="13">
-        <v>46132</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="15">
-        <v>427.82</v>
-      </c>
-      <c r="D20" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E20" s="16">
-        <v>517</v>
-      </c>
-      <c r="F20" s="15">
-        <v>102</v>
-      </c>
-      <c r="G20" s="15">
-        <v>59</v>
-      </c>
-      <c r="H20" s="15">
-        <v>27</v>
-      </c>
-      <c r="I20" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J20" s="18">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="13">
-        <v>46145</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="15">
-        <v>212.92</v>
-      </c>
-      <c r="D21" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E21" s="16">
-        <v>210</v>
-      </c>
-      <c r="F21" s="15">
-        <v>39</v>
-      </c>
-      <c r="G21" s="15">
-        <v>12</v>
-      </c>
-      <c r="H21" s="15">
-        <v>7</v>
-      </c>
-      <c r="I21" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J21" s="18">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="13">
-        <v>46148</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="15">
-        <v>446.02</v>
-      </c>
-      <c r="D22" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E22" s="16">
-        <v>500</v>
-      </c>
-      <c r="F22" s="15">
-        <v>123</v>
-      </c>
-      <c r="G22" s="15">
-        <v>46</v>
-      </c>
-      <c r="H22" s="15">
-        <v>14</v>
-      </c>
-      <c r="I22" s="15">
-        <v>4.7</v>
-      </c>
-      <c r="J22" s="18">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="13">
-        <v>46137</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D23" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E23" s="16">
-        <v>322</v>
-      </c>
-      <c r="F23" s="15">
-        <v>56</v>
-      </c>
-      <c r="G23" s="15">
-        <v>9</v>
-      </c>
-      <c r="H23" s="15">
-        <v>7</v>
-      </c>
-      <c r="I23" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J23" s="18">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="13">
-        <v>46140</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D24" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E24" s="16">
-        <v>322</v>
-      </c>
-      <c r="F24" s="15">
-        <v>56</v>
-      </c>
-      <c r="G24" s="15">
-        <v>9</v>
-      </c>
-      <c r="H24" s="15">
-        <v>7</v>
-      </c>
-      <c r="I24" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J24" s="18">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="13">
-        <v>46140</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D25" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E25" s="16">
-        <v>322</v>
-      </c>
-      <c r="F25" s="15">
-        <v>56</v>
-      </c>
-      <c r="G25" s="15">
-        <v>9</v>
-      </c>
-      <c r="H25" s="15">
-        <v>7</v>
-      </c>
-      <c r="I25" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J25" s="18">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="13">
-        <v>46136</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="15">
-        <v>427.82</v>
-      </c>
-      <c r="D26" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E26" s="16">
-        <v>517</v>
-      </c>
-      <c r="F26" s="15">
-        <v>102</v>
-      </c>
-      <c r="G26" s="15">
-        <v>59</v>
-      </c>
-      <c r="H26" s="15">
-        <v>27</v>
-      </c>
-      <c r="I26" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J26" s="18">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="13">
-        <v>46141</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="15">
-        <v>212.92</v>
-      </c>
-      <c r="D27" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E27" s="16">
-        <v>210</v>
-      </c>
-      <c r="F27" s="15">
-        <v>39</v>
-      </c>
-      <c r="G27" s="15">
-        <v>12</v>
-      </c>
-      <c r="H27" s="15">
-        <v>7</v>
-      </c>
-      <c r="I27" s="15">
-        <v>6.18</v>
-      </c>
-      <c r="J27" s="18">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="13">
-        <v>46138</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="15">
-        <v>446.02</v>
-      </c>
-      <c r="D28" s="16">
-        <v>1000</v>
-      </c>
-      <c r="E28" s="16">
-        <v>500</v>
-      </c>
-      <c r="F28" s="15">
-        <v>123</v>
-      </c>
-      <c r="G28" s="15">
-        <v>46</v>
-      </c>
-      <c r="H28" s="15">
-        <v>14</v>
-      </c>
-      <c r="I28" s="15">
-        <v>4.7</v>
-      </c>
-      <c r="J28" s="18">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="13">
-        <v>46136</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="15">
-        <v>337.91</v>
-      </c>
-      <c r="D29" s="16">
-        <v>1200</v>
-      </c>
-      <c r="E29" s="16">
-        <v>322</v>
-      </c>
-      <c r="F29" s="15">
-        <v>56</v>
-      </c>
-      <c r="G29" s="15">
-        <v>9</v>
-      </c>
-      <c r="H29" s="15">
-        <v>7</v>
-      </c>
-      <c r="I29" s="15">
-        <v>5.31</v>
-      </c>
-      <c r="J29" s="18">
-        <v>2.39</v>
+      <c r="M29" s="41">
+        <v>2</v>
+      </c>
+      <c r="N29" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="O29" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="P29" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q29" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="R29" s="43">
+        <v>0</v>
+      </c>
+      <c r="S29" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="T29" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="U29" s="44">
+        <v>24.06</v>
+      </c>
+      <c r="V29" s="44">
+        <v>0</v>
+      </c>
+      <c r="W29" s="44">
+        <v>0</v>
+      </c>
+      <c r="X29" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y29" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z29" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="P5" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P6" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P7" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P8" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P9" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P10" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P11" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P12" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P13" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P14" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P15" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P16" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P17" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P18" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P19" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P20" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P21" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P22" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P23" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P24" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P25" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P26" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P27" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P28" r:id="rId1" display="1124-4-mcc"/>
+    <hyperlink ref="P29" r:id="rId1" display="1124-4-mcc"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
